--- a/Output/gls_model_all_weekly_output.xlsx
+++ b/Output/gls_model_all_weekly_output.xlsx
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -12066,7 +12066,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.8766 (1.6777, 2.0754)</t>
+          <t>1.8766
+ (1.6777, 2.0754)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -12076,7 +12077,8 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.0045 (-0.0073, -0.0017)</t>
+          <t>-0.0045
+ (-0.0073, -0.0017)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12086,7 +12088,8 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.1905 (-0.0128, 0.3939)</t>
+          <t>0.1905
+ (-0.0128, 0.3939)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12096,7 +12099,8 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0037 (-0.0018, 0.0093)</t>
+          <t>0.0037
+ (-0.0018, 0.0093)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -12106,7 +12110,8 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1253 (-0.0773, 0.3279)</t>
+          <t>0.1253
+ (-0.0773, 0.3279)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -12116,7 +12121,8 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.0015 (-0.0070, 0.0040)</t>
+          <t>-0.0015
+ (-0.0070, 0.0040)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -12138,7 +12144,8 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.9619 (1.8315, 2.0924)</t>
+          <t>1.9619
+ (1.8315, 2.0924)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -12148,7 +12155,8 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0035 (0.0014, 0.0056)</t>
+          <t>0.0035
+ (0.0014, 0.0056)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12158,7 +12166,8 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.4071 (0.1483, 0.6659)</t>
+          <t>0.4071
+ (0.1483, 0.6659)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -12168,7 +12177,8 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0016 (-0.0023, 0.0055)</t>
+          <t>0.0016
+ (-0.0023, 0.0055)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -12178,7 +12188,8 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.3433 (0.0862, 0.6003)</t>
+          <t>0.3433
+ (0.0862, 0.6003)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -12188,7 +12199,8 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.0138 (-0.0177, -0.0099)</t>
+          <t>-0.0138
+ (-0.0177, -0.0099)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -12210,7 +12222,8 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>74.2951 (72.9151, 75.6751)</t>
+          <t>74.2951
+ (72.9151, 75.6751)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -12220,7 +12233,8 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0322 (0.0121, 0.0522)</t>
+          <t>0.0322
+ (0.0121, 0.0522)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12230,7 +12244,8 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.4718 (-4.2835, -0.6601)</t>
+          <t>-2.4718
+ (-4.2835, -0.6601)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -12240,7 +12255,8 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.0241 (-0.0629, 0.0148)</t>
+          <t>-0.0241
+ (-0.0629, 0.0148)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -12250,7 +12266,8 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.2200 (-2.0235, 1.5835)</t>
+          <t>-0.2200
+ (-2.0235, 1.5835)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -12260,7 +12277,8 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0103 (-0.0285, 0.0491)</t>
+          <t>0.0103
+ (-0.0285, 0.0491)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -12282,7 +12300,8 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21.7773 (20.5812, 22.9734)</t>
+          <t>21.7773
+ (20.5812, 22.9734)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12292,7 +12311,8 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.0295 (-0.0468, -0.0121)</t>
+          <t>-0.0295
+ (-0.0468, -0.0121)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -12302,7 +12322,8 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.6701 (0.1177, 3.2224)</t>
+          <t>1.6701
+ (0.1177, 3.2224)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -12312,7 +12333,8 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0180 (-0.0155, 0.0516)</t>
+          <t>0.0180
+ (-0.0155, 0.0516)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -12322,7 +12344,8 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.1605 (-1.7059, 1.3849)</t>
+          <t>-0.1605
+ (-1.7059, 1.3849)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -12332,7 +12355,8 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.0030 (-0.0306, 0.0365)</t>
+          <t>0.0030
+ (-0.0306, 0.0365)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -12354,7 +12378,8 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.2240 (0.2027, 0.2453)</t>
+          <t>0.2240
+ (0.2027, 0.2453)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12364,7 +12389,8 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.0012 (-0.0016, -0.0009)</t>
+          <t>-0.0012
+ (-0.0016, -0.0009)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -12374,7 +12400,8 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.0373 (-0.0826, 0.0079)</t>
+          <t>-0.0373
+ (-0.0826, 0.0079)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12384,7 +12411,8 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0029 (0.0023, 0.0034)</t>
+          <t>0.0029
+ (0.0023, 0.0034)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -12394,7 +12422,8 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0441 (-0.0008, 0.0890)</t>
+          <t>0.0441
+ (-0.0008, 0.0890)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -12404,7 +12433,8 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.0005 (-0.0010, 0.0001)</t>
+          <t>-0.0005
+ (-0.0010, 0.0001)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -12426,7 +12456,8 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.3964 (4.0633, 4.7295)</t>
+          <t>4.3964
+ (4.0633, 4.7295)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12436,7 +12467,8 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0130 (0.0081, 0.0179)</t>
+          <t>0.0130
+ (0.0081, 0.0179)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -12446,7 +12478,8 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.1535 (-1.6304, -0.6766)</t>
+          <t>-1.1535
+ (-1.6304, -0.6766)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12456,7 +12489,8 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0168 (0.0073, 0.0264)</t>
+          <t>0.0168
+ (0.0073, 0.0264)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -12466,7 +12500,8 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0610 (-0.4136, 0.5356)</t>
+          <t>0.0610
+ (-0.4136, 0.5356)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -12476,7 +12511,8 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-0.0390 (-0.0485, -0.0294)</t>
+          <t>-0.0390
+ (-0.0485, -0.0294)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -12498,7 +12534,8 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.5546 (3.8715, 5.2378)</t>
+          <t>4.5546
+ (3.8715, 5.2378)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -12508,7 +12545,8 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0019 (-0.0076, 0.0113)</t>
+          <t>0.0019
+ (-0.0076, 0.0113)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -12518,7 +12556,8 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.7442 (-1.3571, -0.1314)</t>
+          <t>-0.7442
+ (-1.3571, -0.1314)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -12528,7 +12567,8 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0032 (-0.0155, 0.0220)</t>
+          <t>0.0032
+ (-0.0155, 0.0220)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -12538,7 +12578,8 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-0.0013 (-0.6116, 0.6090)</t>
+          <t>-0.0013
+ (-0.6116, 0.6090)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -12548,7 +12589,8 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.0012 (-0.0199, 0.0175)</t>
+          <t>-0.0012
+ (-0.0199, 0.0175)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -12570,7 +12612,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.6465 (5.1048, 6.1881)</t>
+          <t>5.6465
+ (5.1048, 6.1881)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12580,7 +12623,8 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.0108 (-0.0181, -0.0035)</t>
+          <t>-0.0108
+ (-0.0181, -0.0035)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -12590,7 +12634,8 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.6081 (0.2366, 0.9795)</t>
+          <t>0.6081
+ (0.2366, 0.9795)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -12600,7 +12645,8 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0061 (-0.0087, 0.0210)</t>
+          <t>0.0061
+ (-0.0087, 0.0210)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -12610,7 +12656,8 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.0780 (-0.2917, 0.4478)</t>
+          <t>0.0780
+ (-0.2917, 0.4478)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -12620,7 +12667,8 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0290 (0.0141, 0.0438)</t>
+          <t>0.0290
+ (0.0141, 0.0438)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -12642,7 +12690,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.2835 (3.9779, 4.5891)</t>
+          <t>4.2835
+ (3.9779, 4.5891)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12652,7 +12701,8 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.0112 (-0.0162, -0.0063)</t>
+          <t>-0.0112
+ (-0.0162, -0.0063)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -12662,7 +12712,8 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.5666 (0.9760, 2.1572)</t>
+          <t>1.5666
+ (0.9760, 2.1572)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -12672,7 +12723,8 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.0003 (-0.0097, 0.0092)</t>
+          <t>-0.0003
+ (-0.0097, 0.0092)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -12682,7 +12734,8 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.2221 (-0.3648, 0.8089)</t>
+          <t>0.2221
+ (-0.3648, 0.8089)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -12692,7 +12745,8 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0101 (0.0007, 0.0196)</t>
+          <t>0.0101
+ (0.0007, 0.0196)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -12714,7 +12768,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7.3711 (6.6005, 8.1417)</t>
+          <t>7.3711
+ (6.6005, 8.1417)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12724,7 +12779,8 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0379 (0.0257, 0.0501)</t>
+          <t>0.0379
+ (0.0257, 0.0501)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -12734,7 +12790,8 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.4101 (-1.7188, 0.8986)</t>
+          <t>-0.4101
+ (-1.7188, 0.8986)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -12744,7 +12801,8 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.0261 (-0.0491, -0.0031)</t>
+          <t>-0.0261
+ (-0.0491, -0.0031)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -12754,7 +12812,8 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-0.5722 (-1.8739, 0.7295)</t>
+          <t>-0.5722
+ (-1.8739, 0.7295)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -12764,7 +12823,8 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-0.0098 (-0.0328, 0.0132)</t>
+          <t>-0.0098
+ (-0.0328, 0.0132)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -12786,7 +12846,8 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.5899 (0.5308, 0.6491)</t>
+          <t>0.5899
+ (0.5308, 0.6491)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12796,7 +12857,8 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.0030 (-0.0038, -0.0021)</t>
+          <t>-0.0030
+ (-0.0038, -0.0021)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -12806,7 +12868,8 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.1468 (0.0643, 0.2294)</t>
+          <t>0.1468
+ (0.0643, 0.2294)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -12816,7 +12879,8 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0038 (0.0021, 0.0055)</t>
+          <t>0.0038
+ (0.0021, 0.0055)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -12826,7 +12890,8 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.1550 (0.0729, 0.2371)</t>
+          <t>0.1550
+ (0.0729, 0.2371)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -12836,7 +12901,8 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-0.0035 (-0.0052, -0.0018)</t>
+          <t>-0.0035
+ (-0.0052, -0.0018)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -12853,12 +12919,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.2486 (1.0160, 1.4813)</t>
+          <t>1.2486
+ (1.0160, 1.4813)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12868,7 +12935,8 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-0.0039 (-0.0073, -0.0005)</t>
+          <t>-0.0039
+ (-0.0073, -0.0005)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -12878,7 +12946,8 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.4919 (0.1617, 0.8220)</t>
+          <t>0.4919
+ (0.1617, 0.8220)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -12888,7 +12957,8 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.0015 (-0.0081, 0.0052)</t>
+          <t>-0.0015
+ (-0.0081, 0.0052)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -12898,7 +12968,8 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.0791 (-0.2495, 0.4076)</t>
+          <t>0.0791
+ (-0.2495, 0.4076)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -12908,7 +12979,8 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.0029 (-0.0037, 0.0096)</t>
+          <t>0.0029
+ (-0.0037, 0.0096)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -12930,7 +13002,8 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.6961 (0.4298, 0.9623)</t>
+          <t>0.6961
+ (0.4298, 0.9623)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -12940,7 +13013,8 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.0018 (-0.0019, 0.0056)</t>
+          <t>0.0018
+ (-0.0019, 0.0056)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -12950,7 +13024,8 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.1572 (-0.4515, 0.1371)</t>
+          <t>-0.1572
+ (-0.4515, 0.1371)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -12960,7 +13035,8 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0063 (-0.0011, 0.0136)</t>
+          <t>0.0063
+ (-0.0011, 0.0136)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -12970,7 +13046,8 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-0.2152 (-0.5083, 0.0779)</t>
+          <t>-0.2152
+ (-0.5083, 0.0779)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -12980,7 +13057,8 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-0.0135 (-0.0208, -0.0061)</t>
+          <t>-0.0135
+ (-0.0208, -0.0061)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -13002,7 +13080,8 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.2784 (0.2397, 0.3171)</t>
+          <t>0.2784
+ (0.2397, 0.3171)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -13012,7 +13091,8 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-0.0002 (-0.0008, 0.0003)</t>
+          <t>-0.0002
+ (-0.0008, 0.0003)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13022,7 +13102,8 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0547 (-0.0021, 0.1114)</t>
+          <t>0.0547
+ (-0.0021, 0.1114)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -13032,7 +13113,8 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.0005 (-0.0006, 0.0016)</t>
+          <t>0.0005
+ (-0.0006, 0.0016)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -13042,7 +13124,8 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.0070 (-0.0495, 0.0634)</t>
+          <t>0.0070
+ (-0.0495, 0.0634)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -13052,7 +13135,8 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-0.0004 (-0.0015, 0.0007)</t>
+          <t>-0.0004
+ (-0.0015, 0.0007)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -13074,7 +13158,8 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.7358 (1.5819, 1.8896)</t>
+          <t>1.7358
+ (1.5819, 1.8896)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -13084,7 +13169,8 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.0075 (-0.0097, -0.0052)</t>
+          <t>-0.0075
+ (-0.0097, -0.0052)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -13094,7 +13180,8 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.5405 (0.3295, 0.7515)</t>
+          <t>0.5405
+ (0.3295, 0.7515)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -13104,7 +13191,8 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0081 (0.0037, 0.0125)</t>
+          <t>0.0081
+ (0.0037, 0.0125)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -13114,7 +13202,8 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.0623 (-0.1477, 0.2724)</t>
+          <t>0.0623
+ (-0.1477, 0.2724)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -13124,7 +13213,8 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-0.0002 (-0.0045, 0.0042)</t>
+          <t>-0.0002
+ (-0.0045, 0.0042)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -13146,7 +13236,8 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22.6220 (22.1628, 23.0812)</t>
+          <t>22.6220
+ (22.1628, 23.0812)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -13156,7 +13247,8 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-0.0332 (-0.0406, -0.0258)</t>
+          <t>-0.0332
+ (-0.0406, -0.0258)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -13166,7 +13258,8 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.1267 (1.2196, 3.0337)</t>
+          <t>2.1267
+ (1.2196, 3.0337)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -13176,7 +13269,8 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0029 (-0.0106, 0.0164)</t>
+          <t>0.0029
+ (-0.0106, 0.0164)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -13186,7 +13280,8 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.5677 (-0.3332, 1.4687)</t>
+          <t>0.5677
+ (-0.3332, 1.4687)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -13196,7 +13291,8 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.0087 (-0.0048, 0.0222)</t>
+          <t>0.0087
+ (-0.0048, 0.0222)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -13218,7 +13314,8 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.5439 (0.4368, 0.6511)</t>
+          <t>0.5439
+ (0.4368, 0.6511)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -13228,7 +13325,8 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.0009 (-0.0007, 0.0025)</t>
+          <t>0.0009
+ (-0.0007, 0.0025)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -13238,7 +13336,8 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.1442 (0.0025, 0.2859)</t>
+          <t>0.1442
+ (0.0025, 0.2859)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -13248,7 +13347,8 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0043 (0.0012, 0.0073)</t>
+          <t>0.0043
+ (0.0012, 0.0073)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -13258,7 +13358,8 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.0832 (-0.0578, 0.2242)</t>
+          <t>0.0832
+ (-0.0578, 0.2242)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -13268,7 +13369,8 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-0.0071 (-0.0101, -0.0040)</t>
+          <t>-0.0071
+ (-0.0101, -0.0040)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -13290,7 +13392,8 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.3262 (1.2244, 1.4281)</t>
+          <t>1.3262
+ (1.2244, 1.4281)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -13300,7 +13403,8 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-0.0059 (-0.0074, -0.0045)</t>
+          <t>-0.0059
+ (-0.0074, -0.0045)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -13310,7 +13414,8 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0192 (-0.0958, 0.1342)</t>
+          <t>0.0192
+ (-0.0958, 0.1342)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -13320,7 +13425,8 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0074 (0.0045, 0.0102)</t>
+          <t>0.0074
+ (0.0045, 0.0102)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -13330,7 +13436,8 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.0717 (-0.0429, 0.1862)</t>
+          <t>0.0717
+ (-0.0429, 0.1862)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -13340,7 +13447,8 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-0.0018 (-0.0047, 0.0010)</t>
+          <t>-0.0018
+ (-0.0047, 0.0010)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -13362,7 +13470,8 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.0673 (3.5532, 4.5815)</t>
+          <t>4.0673
+ (3.5532, 4.5815)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -13372,7 +13481,8 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0041 (-0.0033, 0.0115)</t>
+          <t>0.0041
+ (-0.0033, 0.0115)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -13382,7 +13492,8 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.5127 (-0.1349, 1.1602)</t>
+          <t>0.5127
+ (-0.1349, 1.1602)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -13392,7 +13503,8 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0095 (-0.0050, 0.0240)</t>
+          <t>0.0095
+ (-0.0050, 0.0240)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -13402,7 +13514,8 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-0.2237 (-0.8684, 0.4210)</t>
+          <t>-0.2237
+ (-0.8684, 0.4210)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -13412,7 +13525,8 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-0.0239 (-0.0384, -0.0094)</t>
+          <t>-0.0239
+ (-0.0384, -0.0094)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -13434,7 +13548,8 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.7849 (1.6401, 1.9297)</t>
+          <t>1.7849
+ (1.6401, 1.9297)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -13444,7 +13559,8 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-0.0002 (-0.0024, 0.0019)</t>
+          <t>-0.0002
+ (-0.0024, 0.0019)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -13454,7 +13570,8 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.1368 (-0.0571, 0.3307)</t>
+          <t>0.1368
+ (-0.0571, 0.3307)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -13464,7 +13581,8 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.0021 (-0.0062, 0.0021)</t>
+          <t>-0.0021
+ (-0.0062, 0.0021)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -13474,7 +13592,8 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.0825 (-0.1105, 0.2755)</t>
+          <t>0.0825
+ (-0.1105, 0.2755)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -13484,7 +13603,8 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.0035 (-0.0006, 0.0076)</t>
+          <t>0.0035
+ (-0.0006, 0.0076)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -13501,12 +13621,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>39.5819 (38.0808, 41.0830)</t>
+          <t>39.5819
+ (38.0808, 41.0830)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -13516,7 +13637,8 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0002 (-0.0231, 0.0235)</t>
+          <t>0.0002
+ (-0.0231, 0.0235)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -13526,7 +13648,8 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.1491 (-3.5038, 1.2057)</t>
+          <t>-1.1491
+ (-3.5038, 1.2057)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -13536,7 +13659,8 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.0608 (-0.1041, -0.0174)</t>
+          <t>-0.0608
+ (-0.1041, -0.0174)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -13546,7 +13670,8 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.2823 (-1.0610, 3.6256)</t>
+          <t>1.2823
+ (-1.0610, 3.6256)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -13556,7 +13681,8 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.0747 (0.0314, 0.1181)</t>
+          <t>0.0747
+ (0.0314, 0.1181)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -13578,7 +13704,8 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>532.2056 (503.1463, 561.2650)</t>
+          <t>532.2056
+ (503.1463, 561.2650)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -13588,7 +13715,8 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.6648 (0.2499, 1.0797)</t>
+          <t>0.6648
+ (0.2499, 1.0797)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -13598,7 +13726,8 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.1722 (-34.1237, 33.7794)</t>
+          <t>-0.1722
+ (-34.1237, 33.7794)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -13608,7 +13737,8 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.0314 (-0.8450, 0.7821)</t>
+          <t>-0.0314
+ (-0.8450, 0.7821)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -13618,7 +13748,8 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-8.1101 (-41.9199, 25.6997)</t>
+          <t>-8.1101
+ (-41.9199, 25.6997)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -13628,7 +13759,8 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-0.8247 (-1.6382, -0.0112)</t>
+          <t>-0.8247
+ (-1.6382, -0.0112)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -13650,7 +13782,8 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>38.9262 (37.4737, 40.3787)</t>
+          <t>38.9262
+ (37.4737, 40.3787)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -13660,7 +13793,8 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-0.0068 (-0.0273, 0.0137)</t>
+          <t>-0.0068
+ (-0.0273, 0.0137)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13670,7 +13804,8 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.9686 (-2.5368, 0.5996)</t>
+          <t>-0.9686
+ (-2.5368, 0.5996)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -13680,7 +13815,8 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.0112 (-0.0290, 0.0514)</t>
+          <t>0.0112
+ (-0.0290, 0.0514)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -13690,7 +13826,8 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.2845 (-1.2775, 1.8465)</t>
+          <t>0.2845
+ (-1.2775, 1.8465)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -13700,7 +13837,8 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-0.0105 (-0.0506, 0.0297)</t>
+          <t>-0.0105
+ (-0.0506, 0.0297)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -13722,7 +13860,8 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.2559 (6.1867, 6.3251)</t>
+          <t>6.2559
+ (6.1867, 6.3251)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -13732,7 +13871,8 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-0.0037 (-0.0047, -0.0027)</t>
+          <t>-0.0037
+ (-0.0047, -0.0027)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -13742,7 +13882,8 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.2738 (0.1744, 0.3732)</t>
+          <t>0.2738
+ (0.1744, 0.3732)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -13752,7 +13893,8 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0027 (0.0007, 0.0047)</t>
+          <t>0.0027
+ (0.0007, 0.0047)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -13762,7 +13904,8 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.0677 (-0.0312, 0.1667)</t>
+          <t>0.0677
+ (-0.0312, 0.1667)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -13772,7 +13915,8 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.0015 (-0.0005, 0.0035)</t>
+          <t>0.0015
+ (-0.0005, 0.0035)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -13794,7 +13938,8 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11.4199 (11.0338, 11.8060)</t>
+          <t>11.4199
+ (11.0338, 11.8060)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -13804,7 +13949,8 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0009 (-0.0046, 0.0064)</t>
+          <t>0.0009
+ (-0.0046, 0.0064)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -13814,7 +13960,8 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.2956 (-0.1551, 0.7463)</t>
+          <t>0.2956
+ (-0.1551, 0.7463)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -13824,7 +13971,8 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0102 (-0.0006, 0.0210)</t>
+          <t>0.0102
+ (-0.0006, 0.0210)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -13834,7 +13982,8 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.0154 (-0.4335, 0.4643)</t>
+          <t>0.0154
+ (-0.4335, 0.4643)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -13844,7 +13993,8 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-0.0199 (-0.0307, -0.0091)</t>
+          <t>-0.0199
+ (-0.0307, -0.0091)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -13866,7 +14016,8 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>43.3490 (42.8863, 43.8116)</t>
+          <t>43.3490
+ (42.8863, 43.8116)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -13876,7 +14027,8 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.0103 (0.0028, 0.0177)</t>
+          <t>0.0103
+ (0.0028, 0.0177)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -13886,7 +14038,8 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.0888 (-0.9822, 0.8045)</t>
+          <t>-0.0888
+ (-0.9822, 0.8045)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -13896,7 +14049,8 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.0144 (-0.0281, -0.0007)</t>
+          <t>-0.0144
+ (-0.0281, -0.0007)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -13906,7 +14060,8 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-0.1657 (-1.0533, 0.7219)</t>
+          <t>-0.1657
+ (-1.0533, 0.7219)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -13916,7 +14071,8 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.0182 (0.0044, 0.0319)</t>
+          <t>0.0182
+ (0.0044, 0.0319)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -13938,7 +14094,8 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4.0776 (3.8519, 4.3032)</t>
+          <t>4.0776
+ (3.8519, 4.3032)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -13948,7 +14105,8 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-0.0026 (-0.0058, 0.0007)</t>
+          <t>-0.0026
+ (-0.0058, 0.0007)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -13958,7 +14116,8 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.3828 (0.1101, 0.6555)</t>
+          <t>0.3828
+ (0.1101, 0.6555)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -13968,7 +14127,8 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0026 (-0.0036, 0.0089)</t>
+          <t>0.0026
+ (-0.0036, 0.0089)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -13978,7 +14138,8 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-0.0717 (-0.3434, 0.2000)</t>
+          <t>-0.0717
+ (-0.3434, 0.2000)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -13988,7 +14149,8 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-0.0013 (-0.0076, 0.0049)</t>
+          <t>-0.0013
+ (-0.0076, 0.0049)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -14010,7 +14172,8 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20.4396 (18.8550, 22.0242)</t>
+          <t>20.4396
+ (18.8550, 22.0242)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -14020,7 +14183,8 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.0137 (-0.0084, 0.0359)</t>
+          <t>0.0137
+ (-0.0084, 0.0359)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -14030,7 +14194,8 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.2700 (-0.3127, 2.8527)</t>
+          <t>1.2700
+ (-0.3127, 2.8527)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -14040,7 +14205,8 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.0216 (-0.0653, 0.0220)</t>
+          <t>-0.0216
+ (-0.0653, 0.0220)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -14050,7 +14216,8 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.9792 (-0.5969, 2.5553)</t>
+          <t>0.9792
+ (-0.5969, 2.5553)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -14060,7 +14227,8 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-0.0029 (-0.0465, 0.0408)</t>
+          <t>-0.0029
+ (-0.0465, 0.0408)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -14082,7 +14250,8 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>96.9558 (95.7809, 98.1307)</t>
+          <t>96.9558
+ (95.7809, 98.1307)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -14092,7 +14261,8 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-0.0264 (-0.0454, -0.0074)</t>
+          <t>-0.0264
+ (-0.0454, -0.0074)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -14102,7 +14272,8 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11.4832 (9.0983, 13.8682)</t>
+          <t>11.4832
+ (9.0983, 13.8682)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -14112,7 +14283,8 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.1025 (-0.1368, -0.0682)</t>
+          <t>-0.1025
+ (-0.1368, -0.0682)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -14122,7 +14294,8 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.4178 (0.0495, 4.7862)</t>
+          <t>2.4178
+ (0.0495, 4.7862)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -14132,7 +14305,8 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.0804 (0.0461, 0.1147)</t>
+          <t>0.0804
+ (0.0461, 0.1147)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -14154,7 +14328,8 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2.2153 (2.1339, 2.2967)</t>
+          <t>2.2153
+ (2.1339, 2.2967)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -14164,7 +14339,8 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-0.0019 (-0.0031, -0.0007)</t>
+          <t>-0.0019
+ (-0.0031, -0.0007)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -14174,7 +14350,8 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.1427 (0.0258, 0.2595)</t>
+          <t>0.1427
+ (0.0258, 0.2595)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -14184,7 +14361,8 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.0012 (-0.0011, 0.0036)</t>
+          <t>0.0012
+ (-0.0011, 0.0036)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -14194,7 +14372,8 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.0319 (-0.0844, 0.1482)</t>
+          <t>0.0319
+ (-0.0844, 0.1482)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -14204,7 +14383,8 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.0006 (-0.0017, 0.0030)</t>
+          <t>0.0006
+ (-0.0017, 0.0030)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -14226,7 +14406,8 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>34.8815 (33.8737, 35.8892)</t>
+          <t>34.8815
+ (33.8737, 35.8892)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -14236,7 +14417,8 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-0.0203 (-0.0351, -0.0055)</t>
+          <t>-0.0203
+ (-0.0351, -0.0055)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14246,7 +14428,8 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.9282 (1.5134, 4.3430)</t>
+          <t>2.9282
+ (1.5134, 4.3430)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -14256,7 +14439,8 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.0098 (-0.0190, 0.0387)</t>
+          <t>0.0098
+ (-0.0190, 0.0387)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -14266,7 +14450,8 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.5399 (-0.8680, 1.9478)</t>
+          <t>0.5399
+ (-0.8680, 1.9478)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -14276,7 +14461,8 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.0045 (-0.0244, 0.0333)</t>
+          <t>0.0045
+ (-0.0244, 0.0333)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -14298,7 +14484,8 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>135.7179 (130.8101, 140.6256)</t>
+          <t>135.7179
+ (130.8101, 140.6256)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -14308,7 +14495,8 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-0.0004 (-0.0723, 0.0716)</t>
+          <t>-0.0004
+ (-0.0723, 0.0716)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -14318,7 +14506,8 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11.1537 (4.3685, 17.9388)</t>
+          <t>11.1537
+ (4.3685, 17.9388)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -14328,7 +14517,8 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.0785 (-0.2184, 0.0614)</t>
+          <t>-0.0785
+ (-0.2184, 0.0614)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -14338,7 +14528,8 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.8781 (-3.8749, 9.6312)</t>
+          <t>2.8781
+ (-3.8749, 9.6312)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -14348,7 +14539,8 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.0087 (-0.1312, 0.1486)</t>
+          <t>0.0087
+ (-0.1312, 0.1486)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -14370,7 +14562,8 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>306.8534 (298.0547, 315.6521)</t>
+          <t>306.8534
+ (298.0547, 315.6521)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -14380,7 +14573,8 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>-0.1702 (-0.2994, -0.0410)</t>
+          <t>-0.1702
+ (-0.2994, -0.0410)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -14390,7 +14584,8 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>28.3364 (16.0789, 40.5940)</t>
+          <t>28.3364
+ (16.0789, 40.5940)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -14400,7 +14595,8 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.0512 (-0.2005, 0.3029)</t>
+          <t>0.0512
+ (-0.2005, 0.3029)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -14410,7 +14606,8 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.4704 (-11.7287, 12.6694)</t>
+          <t>0.4704
+ (-11.7287, 12.6694)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -14420,7 +14617,8 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>-0.0723 (-0.3239, 0.1794)</t>
+          <t>-0.0723
+ (-0.3239, 0.1794)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -14442,7 +14640,8 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>338.8413 (316.5386, 361.1441)</t>
+          <t>338.8413
+ (316.5386, 361.1441)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -14452,7 +14651,8 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-0.5827 (-0.9077, -0.2578)</t>
+          <t>-0.5827
+ (-0.9077, -0.2578)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -14462,7 +14662,8 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>55.7834 (26.2428, 85.3240)</t>
+          <t>55.7834
+ (26.2428, 85.3240)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -14472,7 +14673,8 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-0.2257 (-0.8552, 0.4039)</t>
+          <t>-0.2257
+ (-0.8552, 0.4039)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -14482,7 +14684,8 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19.0765 (-10.3370, 48.4899)</t>
+          <t>19.0765
+ (-10.3370, 48.4899)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -14492,7 +14695,8 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.8018 (0.1722, 1.4313)</t>
+          <t>0.8018
+ (0.1722, 1.4313)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -14514,7 +14718,8 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.7533 (0.7352, 0.7714)</t>
+          <t>0.7533
+ (0.7352, 0.7714)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -14524,7 +14729,8 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-0.0001 (-0.0003, 0.0002)</t>
+          <t>-0.0001
+ (-0.0003, 0.0002)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -14534,7 +14740,8 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.0373 (0.0130, 0.0616)</t>
+          <t>0.0373
+ (0.0130, 0.0616)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -14544,7 +14751,8 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.0001 (-0.0004, 0.0006)</t>
+          <t>0.0001
+ (-0.0004, 0.0006)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -14554,7 +14762,8 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.0106 (-0.0136, 0.0347)</t>
+          <t>0.0106
+ (-0.0136, 0.0347)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -14564,7 +14773,8 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-0.0001 (-0.0006, 0.0004)</t>
+          <t>-0.0001
+ (-0.0006, 0.0004)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -14586,7 +14796,8 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6.6205 (6.5188, 6.7222)</t>
+          <t>6.6205
+ (6.5188, 6.7222)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -14596,7 +14807,8 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-0.0044 (-0.0059, -0.0029)</t>
+          <t>-0.0044
+ (-0.0059, -0.0029)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -14606,7 +14818,8 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.1995 (0.0524, 0.3466)</t>
+          <t>0.1995
+ (0.0524, 0.3466)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -14616,7 +14829,8 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.0057 (0.0028, 0.0086)</t>
+          <t>0.0057
+ (0.0028, 0.0086)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -14626,7 +14840,8 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.2112 (0.0648, 0.3576)</t>
+          <t>0.2112
+ (0.0648, 0.3576)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -14636,7 +14851,8 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.0000 (-0.0030, 0.0029)</t>
+          <t>0.0000
+ (-0.0030, 0.0029)</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -14658,7 +14874,8 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>167.3124 (159.9337, 174.6912)</t>
+          <t>167.3124
+ (159.9337, 174.6912)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -14668,7 +14885,8 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-0.4778 (-0.5873, -0.3684)</t>
+          <t>-0.4778
+ (-0.5873, -0.3684)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -14678,7 +14896,8 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18.3207 (7.4157, 29.2258)</t>
+          <t>18.3207
+ (7.4157, 29.2258)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -14688,7 +14907,8 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.3077 (0.0947, 0.5207)</t>
+          <t>0.3077
+ (0.0947, 0.5207)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -14698,7 +14918,8 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3.1252 (-7.7245, 13.9749)</t>
+          <t>3.1252
+ (-7.7245, 13.9749)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -14708,7 +14929,8 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.1264 (-0.0866, 0.3394)</t>
+          <t>0.1264
+ (-0.0866, 0.3394)</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -14730,7 +14952,8 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.1827 (0.1801, 0.1853)</t>
+          <t>0.1827
+ (0.1801, 0.1853)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -14740,7 +14963,8 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-0.0002 (-0.0002, -0.0001)</t>
+          <t>-0.0002
+ (-0.0002, -0.0001)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -14750,7 +14974,8 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.0035 (-0.0001, 0.0072)</t>
+          <t>0.0035
+ (-0.0001, 0.0072)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -14760,7 +14985,8 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.0002 (0.0001, 0.0002)</t>
+          <t>0.0002
+ (0.0001, 0.0002)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -14770,7 +14996,8 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.0016 (-0.0021, 0.0052)</t>
+          <t>0.0016
+ (-0.0021, 0.0052)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -14780,7 +15007,8 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.0001 (0.0000, 0.0001)</t>
+          <t>0.0001
+ (0.0000, 0.0001)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -14802,7 +15030,8 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.2948 (0.2346, 0.3550)</t>
+          <t>0.2948
+ (0.2346, 0.3550)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -14812,7 +15041,8 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0004 (-0.0005, 0.0012)</t>
+          <t>0.0004
+ (-0.0005, 0.0012)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -14822,7 +15052,8 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.1619 (-0.2407, -0.0830)</t>
+          <t>-0.1619
+ (-0.2407, -0.0830)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -14832,7 +15063,8 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.0003 (-0.0014, 0.0020)</t>
+          <t>0.0003
+ (-0.0014, 0.0020)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -14842,7 +15074,8 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>-0.0126 (-0.0911, 0.0659)</t>
+          <t>-0.0126
+ (-0.0911, 0.0659)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -14852,7 +15085,8 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>-0.0003 (-0.0020, 0.0014)</t>
+          <t>-0.0003
+ (-0.0020, 0.0014)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -14874,7 +15108,8 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2.2130 (2.1697, 2.2563)</t>
+          <t>2.2130
+ (2.1697, 2.2563)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -14884,7 +15119,8 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>-0.0007 (-0.0014, -0.0001)</t>
+          <t>-0.0007
+ (-0.0014, -0.0001)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -14894,7 +15130,8 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.0684 (0.0050, 0.1319)</t>
+          <t>0.0684
+ (0.0050, 0.1319)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -14904,7 +15141,8 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.0015 (0.0003, 0.0028)</t>
+          <t>0.0015
+ (0.0003, 0.0028)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -14914,7 +15152,8 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.0150 (-0.0481, 0.0781)</t>
+          <t>0.0150
+ (-0.0481, 0.0781)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -14924,7 +15163,8 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>-0.0002 (-0.0014, 0.0010)</t>
+          <t>-0.0002
+ (-0.0014, 0.0010)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -14946,7 +15186,8 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>24.4765 (23.2392, 25.7138)</t>
+          <t>24.4765
+ (23.2392, 25.7138)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -14956,7 +15197,8 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-0.0217 (-0.0400, -0.0034)</t>
+          <t>-0.0217
+ (-0.0400, -0.0034)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -14966,7 +15208,8 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.3969 (0.6145, 4.1793)</t>
+          <t>2.3969
+ (0.6145, 4.1793)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -14976,7 +15219,8 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.0150 (-0.0205, 0.0506)</t>
+          <t>0.0150
+ (-0.0205, 0.0506)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -14986,7 +15230,8 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.1585 (-0.6152, 2.9322)</t>
+          <t>1.1585
+ (-0.6152, 2.9322)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -14996,7 +15241,8 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-0.0167 (-0.0523, 0.0188)</t>
+          <t>-0.0167
+ (-0.0523, 0.0188)</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -15018,7 +15264,8 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.5520 (0.5484, 0.5555)</t>
+          <t>0.5520
+ (0.5484, 0.5555)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -15028,7 +15275,8 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-0.0003 (-0.0003, -0.0002)</t>
+          <t>-0.0003
+ (-0.0003, -0.0002)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -15038,7 +15286,8 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.0309 (0.0240, 0.0379)</t>
+          <t>0.0309
+ (0.0240, 0.0379)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -15048,7 +15297,8 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.0003 (0.0002, 0.0004)</t>
+          <t>0.0003
+ (0.0002, 0.0004)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -15058,7 +15308,8 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.0191 (0.0122, 0.0260)</t>
+          <t>0.0191
+ (0.0122, 0.0260)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -15068,7 +15319,8 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-0.0007 (-0.0007, -0.0006)</t>
+          <t>-0.0007
+ (-0.0007, -0.0006)</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -15090,7 +15342,8 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>6.6775 (6.4236, 6.9313)</t>
+          <t>6.6775
+ (6.4236, 6.9313)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -15100,7 +15353,8 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0060 (0.0023, 0.0098)</t>
+          <t>0.0060
+ (0.0023, 0.0098)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -15110,7 +15364,8 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.2193 (-0.1322, 0.5708)</t>
+          <t>0.2193
+ (-0.1322, 0.5708)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -15120,7 +15375,8 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.0117 (-0.0190, -0.0045)</t>
+          <t>-0.0117
+ (-0.0190, -0.0045)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -15130,7 +15386,8 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.1317 (-0.2182, 0.4815)</t>
+          <t>0.1317
+ (-0.2182, 0.4815)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -15140,7 +15397,8 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>-0.0046 (-0.0118, 0.0027)</t>
+          <t>-0.0046
+ (-0.0118, 0.0027)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
